--- a/data/IN/undergrad/people_2013-2014.xlsx
+++ b/data/IN/undergrad/people_2013-2014.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="18528"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="18625"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wscho\Desktop\Test\forge-1.0\data\IN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wscho\Desktop\forge.git\trunk\data\IN\undergrad\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="people" sheetId="1" r:id="rId1"/>
@@ -327,9 +327,6 @@
     <t>district</t>
   </si>
   <si>
-    <t>party</t>
-  </si>
-  <si>
     <t>Candelaria Reardon</t>
   </si>
   <si>
@@ -421,6 +418,9 @@
   </si>
   <si>
     <t>rural_district</t>
+  </si>
+  <si>
+    <t>party_id</t>
   </si>
 </sst>
 </file>
@@ -1289,97 +1289,97 @@
         <v>101</v>
       </c>
       <c r="D1" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="E1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F1" t="s">
         <v>104</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>105</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>106</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>107</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>108</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>109</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>110</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>111</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>112</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>113</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>114</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>115</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>116</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>117</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>118</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>119</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>120</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>121</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>122</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>123</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>124</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>125</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>126</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>127</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>128</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>129</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>130</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
@@ -1696,19 +1696,19 @@
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>5493</v>
+        <v>5494</v>
       </c>
       <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
         <v>6</v>
       </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1723,13 +1723,13 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -1744,7 +1744,7 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1753,66 +1753,66 @@
         <v>0</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5">
         <v>0</v>
       </c>
       <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
         <v>2</v>
       </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>1</v>
-      </c>
-      <c r="AB5">
-        <v>1</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>15</v>
-      </c>
-      <c r="AE5">
-        <v>4</v>
-      </c>
       <c r="AF5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AG5" s="2">
-        <v>560.43785554214787</v>
+        <v>3803.3333333333335</v>
       </c>
       <c r="AH5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>14189</v>
+        <v>5489</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1824,19 +1824,19 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -1878,149 +1878,149 @@
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB6">
         <v>0</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AE6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG6" s="2">
-        <v>1570.0744416873449</v>
+        <v>228.22277210942002</v>
       </c>
       <c r="AH6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>5494</v>
+        <v>5553</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="C7">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
         <v>6</v>
       </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
+      <c r="AE7">
         <v>3</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>1</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>2</v>
       </c>
       <c r="AF7">
         <v>11</v>
       </c>
       <c r="AG7" s="2">
-        <v>3803.3333333333335</v>
+        <v>417.64904919807805</v>
       </c>
       <c r="AH7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>5489</v>
+        <v>5482</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2062,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -2092,19 +2092,19 @@
         <v>0</v>
       </c>
       <c r="AC8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AE8">
+        <v>1</v>
+      </c>
+      <c r="AF8">
         <v>8</v>
       </c>
-      <c r="AE8">
-        <v>6</v>
-      </c>
-      <c r="AF8">
-        <v>14</v>
-      </c>
       <c r="AG8" s="2">
-        <v>228.22277210942002</v>
+        <v>345.64904997604987</v>
       </c>
       <c r="AH8" s="1">
         <v>1</v>
@@ -2112,13 +2112,13 @@
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>5553</v>
+        <v>5532</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -2133,7 +2133,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -2160,13 +2160,13 @@
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9">
         <v>0</v>
       </c>
       <c r="S9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -2193,22 +2193,22 @@
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC9">
         <v>0</v>
       </c>
       <c r="AD9">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF9">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG9" s="2">
-        <v>417.64904919807805</v>
+        <v>1039.214433977327</v>
       </c>
       <c r="AH9" s="1">
         <v>1</v>
@@ -2216,13 +2216,13 @@
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>5482</v>
+        <v>5516</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="C10">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2258,7 +2258,7 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -2270,7 +2270,7 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10">
         <v>0</v>
@@ -2300,33 +2300,27 @@
         <v>0</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD10">
-        <v>1</v>
-      </c>
-      <c r="AE10">
-        <v>1</v>
-      </c>
-      <c r="AF10">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AG10" s="2">
-        <v>345.64904997604987</v>
+        <v>3570.3542234332422</v>
       </c>
       <c r="AH10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>5532</v>
+        <v>5492</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="C11">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -2344,102 +2338,102 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
         <v>3</v>
       </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <v>0</v>
-      </c>
-      <c r="X11">
-        <v>0</v>
-      </c>
-      <c r="Y11">
-        <v>0</v>
-      </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>1</v>
-      </c>
-      <c r="AC11">
-        <v>0</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <v>5</v>
-      </c>
       <c r="AF11">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AG11" s="2">
-        <v>1039.214433977327</v>
+        <v>1857.1428571428571</v>
       </c>
       <c r="AH11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>14765</v>
+        <v>5552</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="C12">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2448,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2466,7 +2460,7 @@
         <v>0</v>
       </c>
       <c r="O12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -2475,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="R12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -2487,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="V12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12">
         <v>0</v>
@@ -2502,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB12">
         <v>0</v>
@@ -2514,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="AG12" s="2">
-        <v>165.49053356282272</v>
+        <v>654.39627228525126</v>
       </c>
       <c r="AH12" s="1">
         <v>1</v>
@@ -2522,22 +2516,22 @@
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>5516</v>
+        <v>5508</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="C13">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2564,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="O13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -2603,7 +2597,7 @@
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC13">
         <v>1</v>
@@ -2611,8 +2605,14 @@
       <c r="AD13">
         <v>0</v>
       </c>
+      <c r="AE13">
+        <v>2</v>
+      </c>
+      <c r="AF13">
+        <v>9</v>
+      </c>
       <c r="AG13" s="2">
-        <v>3570.3542234332422</v>
+        <v>2125.8474576271187</v>
       </c>
       <c r="AH13" s="1">
         <v>0</v>
@@ -2620,117 +2620,117 @@
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>14192</v>
+        <v>5624</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="C14">
+        <v>34</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>3</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>5</v>
+      </c>
+      <c r="AF14">
         <v>13</v>
       </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <v>1</v>
-      </c>
-      <c r="AD14">
-        <v>17</v>
-      </c>
-      <c r="AE14">
-        <v>7</v>
-      </c>
-      <c r="AF14">
-        <v>3</v>
-      </c>
       <c r="AG14" s="2">
-        <v>36.290752408256232</v>
+        <v>2503.2308291163872</v>
       </c>
       <c r="AH14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>5492</v>
+        <v>5499</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C15">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -2748,96 +2748,96 @@
         <v>0</v>
       </c>
       <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
         <v>3</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <v>1</v>
-      </c>
-      <c r="R15">
-        <v>1</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>0</v>
-      </c>
-      <c r="AC15">
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <v>0</v>
       </c>
       <c r="AE15">
         <v>3</v>
       </c>
       <c r="AF15">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AG15" s="2">
-        <v>1857.1428571428571</v>
+        <v>850.13806706114406</v>
       </c>
       <c r="AH15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>14766</v>
+        <v>5498</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="C16">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T16">
         <v>0</v>
@@ -2897,13 +2897,13 @@
         <v>0</v>
       </c>
       <c r="X16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA16">
         <v>0</v>
@@ -2918,30 +2918,30 @@
         <v>0</v>
       </c>
       <c r="AE16">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AF16">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG16" s="2">
-        <v>1723.618895116093</v>
+        <v>647.82778864970646</v>
       </c>
       <c r="AH16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>5570</v>
+        <v>5563</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C17">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -2956,13 +2956,13 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -3010,10 +3010,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -3021,14 +3021,8 @@
       <c r="AD17">
         <v>0</v>
       </c>
-      <c r="AE17">
-        <v>4</v>
-      </c>
-      <c r="AF17">
-        <v>2</v>
-      </c>
       <c r="AG17" s="2">
-        <v>48.998578530546553</v>
+        <v>71.950715935850369</v>
       </c>
       <c r="AH17" s="1">
         <v>1</v>
@@ -3036,16 +3030,16 @@
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>14438</v>
+        <v>5549</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="C18">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -3057,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -3069,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -3078,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="O18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -3087,7 +3081,7 @@
         <v>0</v>
       </c>
       <c r="R18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -3102,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X18">
         <v>0</v>
@@ -3114,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB18">
         <v>0</v>
@@ -3126,30 +3120,30 @@
         <v>0</v>
       </c>
       <c r="AE18">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AF18">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG18" s="2">
-        <v>95.181540549711585</v>
+        <v>2020.6172839506173</v>
       </c>
       <c r="AH18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>5546</v>
+        <v>5528</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C19">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -3167,76 +3161,76 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>1</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
         <v>2</v>
       </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>1</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>0</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>0</v>
-      </c>
-      <c r="V19">
-        <v>0</v>
-      </c>
-      <c r="W19">
-        <v>0</v>
-      </c>
-      <c r="X19">
-        <v>0</v>
-      </c>
-      <c r="Y19">
-        <v>0</v>
-      </c>
-      <c r="Z19">
-        <v>0</v>
-      </c>
-      <c r="AA19">
-        <v>0</v>
-      </c>
-      <c r="AB19">
-        <v>0</v>
-      </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
-      <c r="AE19">
-        <v>9</v>
-      </c>
       <c r="AF19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG19" s="2">
-        <v>91.016249426613484</v>
+        <v>142.27939575987114</v>
       </c>
       <c r="AH19" s="1">
         <v>1</v>
@@ -3244,13 +3238,13 @@
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>5552</v>
+        <v>5568</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C20">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -3259,7 +3253,7 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -3268,7 +3262,7 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3298,7 +3292,7 @@
         <v>0</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20">
         <v>0</v>
@@ -3307,13 +3301,13 @@
         <v>0</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20">
         <v>0</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y20">
         <v>0</v>
@@ -3322,42 +3316,48 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB20">
         <v>0</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD20">
         <v>0</v>
       </c>
+      <c r="AE20">
+        <v>5</v>
+      </c>
+      <c r="AF20">
+        <v>14</v>
+      </c>
       <c r="AG20" s="2">
-        <v>654.39627228525126</v>
+        <v>1358.6843743515253</v>
       </c>
       <c r="AH20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>5519</v>
+        <v>5500</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C21">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3378,10 +3378,10 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>0</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3426,36 +3426,36 @@
         <v>0</v>
       </c>
       <c r="AC21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD21">
         <v>0</v>
       </c>
       <c r="AE21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF21">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AG21" s="2">
-        <v>109.92443239001757</v>
+        <v>2478.1923076923076</v>
       </c>
       <c r="AH21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>11394</v>
+        <v>5569</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="C22">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -3476,7 +3476,7 @@
         <v>1</v>
       </c>
       <c r="K22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -3485,10 +3485,10 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -3506,7 +3506,7 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V22">
         <v>0</v>
@@ -3533,33 +3533,33 @@
         <v>0</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE22">
         <v>3</v>
       </c>
       <c r="AF22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AG22" s="2">
-        <v>581.90301761730336</v>
+        <v>3640.5283867341213</v>
       </c>
       <c r="AH22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>10569</v>
+        <v>5533</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="C23">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -3580,13 +3580,13 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -3595,10 +3595,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="Z23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA23">
         <v>0</v>
@@ -3639,31 +3639,37 @@
       <c r="AD23">
         <v>0</v>
       </c>
+      <c r="AE23">
+        <v>4</v>
+      </c>
+      <c r="AF23">
+        <v>10</v>
+      </c>
       <c r="AG23" s="2">
-        <v>165.0660725261217</v>
+        <v>1709.4712525667351</v>
       </c>
       <c r="AH23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>5539</v>
+        <v>14436</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="C24">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3681,7 +3687,7 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -3690,10 +3696,10 @@
         <v>0</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -3723,10 +3729,10 @@
         <v>0</v>
       </c>
       <c r="Z24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB24">
         <v>0</v>
@@ -3735,39 +3741,39 @@
         <v>0</v>
       </c>
       <c r="AD24">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AF24">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AG24" s="2">
-        <v>119.33655915956801</v>
+        <v>2195.8404950154691</v>
       </c>
       <c r="AH24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>14761</v>
+        <v>14440</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C25">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3788,13 +3794,13 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25">
         <v>0</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -3812,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25">
         <v>0</v>
@@ -3833,10 +3839,10 @@
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD25">
         <v>0</v>
@@ -3845,30 +3851,30 @@
         <v>5</v>
       </c>
       <c r="AF25">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AG25" s="2">
-        <v>612.5209861270655</v>
+        <v>3271.7664092664095</v>
       </c>
       <c r="AH25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>5571</v>
+        <v>5543</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C26">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -3889,7 +3895,7 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -3907,19 +3913,19 @@
         <v>0</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S26">
         <v>0</v>
       </c>
       <c r="T26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U26">
         <v>0</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26">
         <v>0</v>
@@ -3940,36 +3946,36 @@
         <v>0</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD26">
         <v>0</v>
       </c>
       <c r="AE26">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AF26">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AG26" s="2">
-        <v>70.766197491647958</v>
+        <v>3888.6512180629838</v>
       </c>
       <c r="AH26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>5515</v>
+        <v>5556</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C27">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -3987,16 +3993,16 @@
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -4011,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="R27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -4044,39 +4050,39 @@
         <v>0</v>
       </c>
       <c r="AC27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG27" s="2">
-        <v>834.55688246385921</v>
+        <v>2822.6678291194416</v>
       </c>
       <c r="AH27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>5508</v>
+        <v>5566</v>
       </c>
       <c r="B28" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="C28">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -4121,7 +4127,7 @@
         <v>0</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U28">
         <v>0</v>
@@ -4145,10 +4151,10 @@
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD28">
         <v>0</v>
@@ -4157,10 +4163,10 @@
         <v>2</v>
       </c>
       <c r="AF28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG28" s="2">
-        <v>2125.8474576271187</v>
+        <v>3396.2848297213632</v>
       </c>
       <c r="AH28" s="1">
         <v>0</v>
@@ -4168,16 +4174,16 @@
     </row>
     <row r="29" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>5560</v>
+        <v>14442</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="C29">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -4192,10 +4198,10 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -4207,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -4219,7 +4225,7 @@
         <v>0</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -4237,7 +4243,7 @@
         <v>0</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29">
         <v>0</v>
@@ -4252,42 +4258,42 @@
         <v>0</v>
       </c>
       <c r="AC29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD29">
         <v>0</v>
       </c>
       <c r="AE29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF29">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AG29" s="2">
-        <v>187.80817972350232</v>
+        <v>2358.7956204379561</v>
       </c>
       <c r="AH29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>5544</v>
+        <v>14446</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="C30">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -4299,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="J30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -4311,7 +4317,7 @@
         <v>0</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -4329,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30">
         <v>0</v>
@@ -4344,7 +4350,7 @@
         <v>1</v>
       </c>
       <c r="Y30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4359,33 +4365,33 @@
         <v>0</v>
       </c>
       <c r="AD30">
+        <v>7</v>
+      </c>
+      <c r="AE30">
+        <v>5</v>
+      </c>
+      <c r="AF30">
         <v>11</v>
       </c>
-      <c r="AE30">
-        <v>7</v>
-      </c>
-      <c r="AF30">
-        <v>7</v>
-      </c>
       <c r="AG30" s="2">
-        <v>561.5861951717103</v>
+        <v>3231.1817279046672</v>
       </c>
       <c r="AH30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>10578</v>
+        <v>5518</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="C31">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -4412,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -4430,7 +4436,7 @@
         <v>0</v>
       </c>
       <c r="S31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T31">
         <v>0</v>
@@ -4445,13 +4451,13 @@
         <v>0</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y31">
         <v>0</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA31">
         <v>0</v>
@@ -4460,36 +4466,36 @@
         <v>0</v>
       </c>
       <c r="AC31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF31">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG31" s="2">
-        <v>337.34063796016591</v>
+        <v>3217.4737893160259</v>
       </c>
       <c r="AH31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>10575</v>
+        <v>14191</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C32">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -4501,7 +4507,7 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -4510,22 +4516,22 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32">
         <v>0</v>
       </c>
       <c r="O32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -4543,7 +4549,7 @@
         <v>0</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W32">
         <v>0</v>
@@ -4561,7 +4567,7 @@
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -4573,24 +4579,24 @@
         <v>4</v>
       </c>
       <c r="AF32">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AG32" s="2">
-        <v>146.40708366443411</v>
+        <v>4090.1774397972126</v>
       </c>
       <c r="AH32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>5559</v>
+        <v>5493</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="C33">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -4611,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -4641,16 +4647,16 @@
         <v>0</v>
       </c>
       <c r="T33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U33">
         <v>0</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X33">
         <v>0</v>
@@ -4662,19 +4668,25 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="AE33">
+        <v>4</v>
+      </c>
+      <c r="AF33">
+        <v>1</v>
       </c>
       <c r="AG33" s="2">
-        <v>91.182399107946992</v>
+        <v>560.43785554214787</v>
       </c>
       <c r="AH33" s="1">
         <v>1</v>
@@ -4682,13 +4694,13 @@
     </row>
     <row r="34" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>5561</v>
+        <v>14189</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="C34">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -4706,19 +4718,19 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -4742,13 +4754,13 @@
         <v>0</v>
       </c>
       <c r="U34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X34">
         <v>0</v>
@@ -4760,7 +4772,7 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB34">
         <v>0</v>
@@ -4771,25 +4783,31 @@
       <c r="AD34">
         <v>0</v>
       </c>
+      <c r="AE34">
+        <v>8</v>
+      </c>
+      <c r="AF34">
+        <v>12</v>
+      </c>
       <c r="AG34" s="2">
-        <v>65.629217783686869</v>
+        <v>1570.0744416873449</v>
       </c>
       <c r="AH34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>5624</v>
+        <v>14765</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="C35">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -4804,7 +4822,7 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -4813,7 +4831,7 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -4822,7 +4840,7 @@
         <v>0</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P35">
         <v>0</v>
@@ -4831,7 +4849,7 @@
         <v>0</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -4840,10 +4858,10 @@
         <v>0</v>
       </c>
       <c r="U35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35">
         <v>0</v>
@@ -4869,34 +4887,28 @@
       <c r="AD35">
         <v>0</v>
       </c>
-      <c r="AE35">
-        <v>5</v>
-      </c>
-      <c r="AF35">
-        <v>13</v>
-      </c>
       <c r="AG35" s="2">
-        <v>2503.2308291163872</v>
+        <v>165.49053356282272</v>
       </c>
       <c r="AH35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>5564</v>
+        <v>14192</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="C36">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="D36">
         <v>1</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -4917,7 +4929,7 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -4944,7 +4956,7 @@
         <v>0</v>
       </c>
       <c r="U36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36">
         <v>0</v>
@@ -4962,19 +4974,25 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB36">
         <v>0</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="AE36">
+        <v>7</v>
+      </c>
+      <c r="AF36">
+        <v>3</v>
       </c>
       <c r="AG36" s="2">
-        <v>208.30542531815144</v>
+        <v>36.290752408256232</v>
       </c>
       <c r="AH36" s="1">
         <v>1</v>
@@ -4982,16 +5000,16 @@
     </row>
     <row r="37" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>5499</v>
+        <v>14766</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C37">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -5027,7 +5045,7 @@
         <v>0</v>
       </c>
       <c r="P37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -5042,16 +5060,16 @@
         <v>0</v>
       </c>
       <c r="U37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37">
         <v>0</v>
       </c>
       <c r="W37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37">
         <v>0</v>
@@ -5066,39 +5084,39 @@
         <v>0</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD37">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AF37">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AG37" s="2">
-        <v>850.13806706114406</v>
+        <v>1723.618895116093</v>
       </c>
       <c r="AH37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>14439</v>
+        <v>5570</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="C38">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="D38">
         <v>1</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -5110,13 +5128,13 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38">
         <v>0</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -5167,36 +5185,36 @@
         <v>0</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD38">
         <v>0</v>
       </c>
       <c r="AE38">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AF38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG38" s="2">
-        <v>1715.9264931087289</v>
+        <v>48.998578530546553</v>
       </c>
       <c r="AH38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>10577</v>
+        <v>14438</v>
       </c>
       <c r="B39" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="C39">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -5211,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -5223,7 +5241,7 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39">
         <v>0</v>
@@ -5232,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P39">
         <v>0</v>
@@ -5268,7 +5286,7 @@
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB39">
         <v>0</v>
@@ -5280,13 +5298,13 @@
         <v>0</v>
       </c>
       <c r="AE39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF39">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG39" s="2">
-        <v>84.453687787852147</v>
+        <v>95.181540549711585</v>
       </c>
       <c r="AH39" s="1">
         <v>1</v>
@@ -5294,13 +5312,13 @@
     </row>
     <row r="40" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>5509</v>
+        <v>5546</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C40">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -5309,7 +5327,7 @@
         <v>0</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -5324,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -5336,13 +5354,13 @@
         <v>0</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -5360,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="W40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X40">
         <v>0</v>
@@ -5384,27 +5402,27 @@
         <v>0</v>
       </c>
       <c r="AE40">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AF40">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG40" s="2">
-        <v>1920.053238686779</v>
+        <v>91.016249426613484</v>
       </c>
       <c r="AH40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>5502</v>
+        <v>5519</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C41">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -5413,13 +5431,13 @@
         <v>0</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -5434,7 +5452,7 @@
         <v>0</v>
       </c>
       <c r="M41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41">
         <v>0</v>
@@ -5446,7 +5464,7 @@
         <v>0</v>
       </c>
       <c r="Q41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R41">
         <v>0</v>
@@ -5470,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="Y41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5482,33 +5500,33 @@
         <v>0</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD41">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AE41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF41">
         <v>6</v>
       </c>
       <c r="AG41" s="2">
-        <v>1248.5231283670817</v>
+        <v>109.92443239001757</v>
       </c>
       <c r="AH41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>5524</v>
+        <v>11394</v>
       </c>
       <c r="B42" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="C42">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -5529,10 +5547,10 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -5544,7 +5562,7 @@
         <v>0</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P42">
         <v>0</v>
@@ -5562,7 +5580,7 @@
         <v>0</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42">
         <v>0</v>
@@ -5586,19 +5604,19 @@
         <v>0</v>
       </c>
       <c r="AC42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD42">
         <v>0</v>
       </c>
       <c r="AE42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG42" s="2">
-        <v>86.012392928740667</v>
+        <v>581.90301761730336</v>
       </c>
       <c r="AH42" s="1">
         <v>1</v>
@@ -5606,19 +5624,19 @@
     </row>
     <row r="43" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>14443</v>
+        <v>10569</v>
       </c>
       <c r="B43" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="C43">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D43">
         <v>1</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -5627,7 +5645,7 @@
         <v>0</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -5636,13 +5654,13 @@
         <v>0</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43">
         <v>0</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N43">
         <v>0</v>
@@ -5660,7 +5678,7 @@
         <v>0</v>
       </c>
       <c r="S43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T43">
         <v>0</v>
@@ -5681,10 +5699,10 @@
         <v>0</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB43">
         <v>0</v>
@@ -5695,14 +5713,8 @@
       <c r="AD43">
         <v>0</v>
       </c>
-      <c r="AE43">
-        <v>6</v>
-      </c>
-      <c r="AF43">
-        <v>4</v>
-      </c>
       <c r="AG43" s="2">
-        <v>71.190999148325787</v>
+        <v>165.0660725261217</v>
       </c>
       <c r="AH43" s="1">
         <v>1</v>
@@ -5710,19 +5722,19 @@
     </row>
     <row r="44" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>5498</v>
+        <v>5539</v>
       </c>
       <c r="B44" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C44">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -5743,7 +5755,7 @@
         <v>0</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44">
         <v>0</v>
@@ -5764,7 +5776,7 @@
         <v>0</v>
       </c>
       <c r="S44">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T44">
         <v>0</v>
@@ -5782,7 +5794,7 @@
         <v>0</v>
       </c>
       <c r="Y44">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z44">
         <v>1</v>
@@ -5794,19 +5806,19 @@
         <v>0</v>
       </c>
       <c r="AC44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF44">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AG44" s="2">
-        <v>647.82778864970646</v>
+        <v>119.33655915956801</v>
       </c>
       <c r="AH44" s="1">
         <v>1</v>
@@ -5814,22 +5826,22 @@
     </row>
     <row r="45" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>10818</v>
+        <v>14761</v>
       </c>
       <c r="B45" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="C45">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -5889,7 +5901,7 @@
         <v>0</v>
       </c>
       <c r="Z45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA45">
         <v>0</v>
@@ -5904,13 +5916,13 @@
         <v>0</v>
       </c>
       <c r="AE45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF45">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG45" s="2">
-        <v>72.390953512350379</v>
+        <v>612.5209861270655</v>
       </c>
       <c r="AH45" s="1">
         <v>1</v>
@@ -5918,19 +5930,19 @@
     </row>
     <row r="46" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>5563</v>
+        <v>5571</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C46">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -5942,16 +5954,16 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46">
         <v>0</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46">
         <v>0</v>
@@ -5975,7 +5987,7 @@
         <v>0</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U46">
         <v>0</v>
@@ -5996,7 +6008,7 @@
         <v>0</v>
       </c>
       <c r="AA46">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB46">
         <v>0</v>
@@ -6007,8 +6019,14 @@
       <c r="AD46">
         <v>0</v>
       </c>
+      <c r="AE46">
+        <v>8</v>
+      </c>
+      <c r="AF46">
+        <v>1</v>
+      </c>
       <c r="AG46" s="2">
-        <v>71.950715935850369</v>
+        <v>70.766197491647958</v>
       </c>
       <c r="AH46" s="1">
         <v>1</v>
@@ -6016,13 +6034,13 @@
     </row>
     <row r="47" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>10574</v>
+        <v>5515</v>
       </c>
       <c r="B47" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="C47">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -6055,22 +6073,22 @@
         <v>0</v>
       </c>
       <c r="N47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q47">
         <v>0</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T47">
         <v>0</v>
@@ -6100,19 +6118,19 @@
         <v>0</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD47">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AE47">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AF47">
         <v>7</v>
       </c>
       <c r="AG47" s="2">
-        <v>94.175462028716197</v>
+        <v>834.55688246385921</v>
       </c>
       <c r="AH47" s="1">
         <v>1</v>
@@ -6120,13 +6138,13 @@
     </row>
     <row r="48" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>14445</v>
+        <v>5560</v>
       </c>
       <c r="B48" t="s">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="C48">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -6144,10 +6162,10 @@
         <v>0</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -6159,7 +6177,7 @@
         <v>0</v>
       </c>
       <c r="N48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -6171,7 +6189,7 @@
         <v>0</v>
       </c>
       <c r="R48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -6201,22 +6219,22 @@
         <v>0</v>
       </c>
       <c r="AB48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD48">
         <v>0</v>
       </c>
       <c r="AE48">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF48">
         <v>2</v>
       </c>
       <c r="AG48" s="2">
-        <v>308.08317332459137</v>
+        <v>187.80817972350232</v>
       </c>
       <c r="AH48" s="1">
         <v>1</v>
@@ -6224,13 +6242,13 @@
     </row>
     <row r="49" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>5512</v>
+        <v>5544</v>
       </c>
       <c r="B49" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C49">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -6251,13 +6269,13 @@
         <v>0</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49">
         <v>0</v>
@@ -6275,7 +6293,7 @@
         <v>0</v>
       </c>
       <c r="R49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -6293,16 +6311,16 @@
         <v>0</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB49">
         <v>0</v>
@@ -6311,10 +6329,16 @@
         <v>0</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="AE49">
+        <v>7</v>
+      </c>
+      <c r="AF49">
+        <v>7</v>
       </c>
       <c r="AG49" s="2">
-        <v>850.61679790026244</v>
+        <v>561.5861951717103</v>
       </c>
       <c r="AH49" s="1">
         <v>1</v>
@@ -6322,13 +6346,13 @@
     </row>
     <row r="50" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>5513</v>
+        <v>10578</v>
       </c>
       <c r="B50" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="C50">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -6337,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -6358,7 +6382,7 @@
         <v>0</v>
       </c>
       <c r="M50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N50">
         <v>0</v>
@@ -6376,7 +6400,7 @@
         <v>0</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T50">
         <v>0</v>
@@ -6391,13 +6415,13 @@
         <v>0</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y50">
         <v>0</v>
       </c>
       <c r="Z50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA50">
         <v>0</v>
@@ -6406,19 +6430,19 @@
         <v>0</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF50">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AG50" s="2">
-        <v>381.26290941280615</v>
+        <v>337.34063796016591</v>
       </c>
       <c r="AH50" s="1">
         <v>1</v>
@@ -6426,13 +6450,13 @@
     </row>
     <row r="51" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>5510</v>
+        <v>10575</v>
       </c>
       <c r="B51" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C51">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -6447,7 +6471,7 @@
         <v>0</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -6462,19 +6486,19 @@
         <v>0</v>
       </c>
       <c r="M51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51">
         <v>0</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51">
         <v>0</v>
@@ -6510,19 +6534,19 @@
         <v>0</v>
       </c>
       <c r="AC51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD51">
         <v>0</v>
       </c>
       <c r="AE51">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AF51">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG51" s="2">
-        <v>115.98528065356714</v>
+        <v>146.40708366443411</v>
       </c>
       <c r="AH51" s="1">
         <v>1</v>
@@ -6530,13 +6554,13 @@
     </row>
     <row r="52" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>14768</v>
+        <v>5559</v>
       </c>
       <c r="B52" t="s">
-        <v>99</v>
+        <v>43</v>
       </c>
       <c r="C52">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -6569,7 +6593,7 @@
         <v>0</v>
       </c>
       <c r="N52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O52">
         <v>0</v>
@@ -6596,7 +6620,7 @@
         <v>0</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X52">
         <v>0</v>
@@ -6611,22 +6635,16 @@
         <v>0</v>
       </c>
       <c r="AB52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD52">
         <v>0</v>
       </c>
-      <c r="AE52">
-        <v>9</v>
-      </c>
-      <c r="AF52">
-        <v>9</v>
-      </c>
       <c r="AG52" s="2">
-        <v>107.59067742095107</v>
+        <v>91.182399107946992</v>
       </c>
       <c r="AH52" s="1">
         <v>1</v>
@@ -6634,13 +6652,13 @@
     </row>
     <row r="53" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>14447</v>
+        <v>5561</v>
       </c>
       <c r="B53" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="C53">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -6649,7 +6667,7 @@
         <v>0</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -6661,10 +6679,10 @@
         <v>0</v>
       </c>
       <c r="J53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -6694,13 +6712,13 @@
         <v>0</v>
       </c>
       <c r="U53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V53">
         <v>1</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X53">
         <v>0</v>
@@ -6723,14 +6741,8 @@
       <c r="AD53">
         <v>0</v>
       </c>
-      <c r="AE53">
-        <v>8</v>
-      </c>
-      <c r="AF53">
-        <v>11</v>
-      </c>
       <c r="AG53" s="2">
-        <v>148.61082806874532</v>
+        <v>65.629217783686869</v>
       </c>
       <c r="AH53" s="1">
         <v>1</v>
@@ -6738,13 +6750,13 @@
     </row>
     <row r="54" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>5527</v>
+        <v>5564</v>
       </c>
       <c r="B54" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C54">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -6771,7 +6783,7 @@
         <v>0</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54">
         <v>0</v>
@@ -6789,7 +6801,7 @@
         <v>0</v>
       </c>
       <c r="R54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54">
         <v>0</v>
@@ -6798,13 +6810,13 @@
         <v>0</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V54">
         <v>0</v>
       </c>
       <c r="W54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X54">
         <v>0</v>
@@ -6813,28 +6825,22 @@
         <v>0</v>
       </c>
       <c r="Z54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB54">
         <v>0</v>
       </c>
       <c r="AC54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD54">
         <v>0</v>
       </c>
-      <c r="AE54">
-        <v>3</v>
-      </c>
-      <c r="AF54">
-        <v>3</v>
-      </c>
       <c r="AG54" s="2">
-        <v>205.43578054262829</v>
+        <v>208.30542531815144</v>
       </c>
       <c r="AH54" s="1">
         <v>1</v>
@@ -6842,13 +6848,13 @@
     </row>
     <row r="55" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>5537</v>
+        <v>14439</v>
       </c>
       <c r="B55" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="C55">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -6866,7 +6872,7 @@
         <v>0</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -6893,10 +6899,10 @@
         <v>0</v>
       </c>
       <c r="R55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T55">
         <v>0</v>
@@ -6905,7 +6911,7 @@
         <v>0</v>
       </c>
       <c r="V55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W55">
         <v>0</v>
@@ -6917,7 +6923,7 @@
         <v>0</v>
       </c>
       <c r="Z55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA55">
         <v>0</v>
@@ -6926,33 +6932,33 @@
         <v>0</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD55">
         <v>0</v>
       </c>
       <c r="AE55">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF55">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AG55" s="2">
-        <v>110.01587408808433</v>
+        <v>1715.9264931087289</v>
       </c>
       <c r="AH55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>14767</v>
+        <v>10577</v>
       </c>
       <c r="B56" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="C56">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -6961,7 +6967,7 @@
         <v>0</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -6979,10 +6985,10 @@
         <v>0</v>
       </c>
       <c r="L56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N56">
         <v>0</v>
@@ -6997,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56">
         <v>0</v>
@@ -7015,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="X56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y56">
         <v>0</v>
@@ -7024,7 +7030,7 @@
         <v>0</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB56">
         <v>0</v>
@@ -7036,13 +7042,13 @@
         <v>0</v>
       </c>
       <c r="AE56">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AF56">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG56" s="2">
-        <v>79.015716973117293</v>
+        <v>84.453687787852147</v>
       </c>
       <c r="AH56" s="1">
         <v>1</v>
@@ -7050,13 +7056,13 @@
     </row>
     <row r="57" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>14437</v>
+        <v>5509</v>
       </c>
       <c r="B57" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="C57">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -7065,7 +7071,7 @@
         <v>0</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -7077,10 +7083,10 @@
         <v>0</v>
       </c>
       <c r="J57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -7089,7 +7095,7 @@
         <v>0</v>
       </c>
       <c r="N57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O57">
         <v>0</v>
@@ -7098,7 +7104,7 @@
         <v>1</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R57">
         <v>0</v>
@@ -7116,7 +7122,7 @@
         <v>0</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X57">
         <v>0</v>
@@ -7125,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="Z57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA57">
         <v>0</v>
@@ -7140,27 +7146,27 @@
         <v>0</v>
       </c>
       <c r="AE57">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AF57">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AG57" s="2">
-        <v>180.06082759005554</v>
+        <v>1920.053238686779</v>
       </c>
       <c r="AH57" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>5573</v>
+        <v>5502</v>
       </c>
       <c r="B58" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="C58">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -7187,10 +7193,10 @@
         <v>0</v>
       </c>
       <c r="L58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N58">
         <v>0</v>
@@ -7202,32 +7208,32 @@
         <v>0</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R58">
         <v>0</v>
       </c>
       <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58">
+        <v>0</v>
+      </c>
+      <c r="U58">
+        <v>0</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0</v>
+      </c>
+      <c r="X58">
+        <v>0</v>
+      </c>
+      <c r="Y58">
         <v>2</v>
       </c>
-      <c r="T58">
-        <v>0</v>
-      </c>
-      <c r="U58">
-        <v>1</v>
-      </c>
-      <c r="V58">
-        <v>0</v>
-      </c>
-      <c r="W58">
-        <v>0</v>
-      </c>
-      <c r="X58">
-        <v>0</v>
-      </c>
-      <c r="Y58">
-        <v>0</v>
-      </c>
       <c r="Z58">
         <v>0</v>
       </c>
@@ -7241,30 +7247,30 @@
         <v>0</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE58">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG58" s="2">
-        <v>113.92783106707424</v>
+        <v>1248.5231283670817</v>
       </c>
       <c r="AH58" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>5536</v>
+        <v>5524</v>
       </c>
       <c r="B59" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C59">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -7282,10 +7288,10 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59">
         <v>0</v>
@@ -7297,64 +7303,64 @@
         <v>0</v>
       </c>
       <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59">
+        <v>0</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0</v>
+      </c>
+      <c r="X59">
+        <v>0</v>
+      </c>
+      <c r="Y59">
+        <v>0</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+      <c r="AA59">
+        <v>0</v>
+      </c>
+      <c r="AB59">
+        <v>0</v>
+      </c>
+      <c r="AC59">
         <v>2</v>
       </c>
-      <c r="O59">
-        <v>0</v>
-      </c>
-      <c r="P59">
-        <v>1</v>
-      </c>
-      <c r="Q59">
-        <v>0</v>
-      </c>
-      <c r="R59">
-        <v>0</v>
-      </c>
-      <c r="S59">
-        <v>0</v>
-      </c>
-      <c r="T59">
-        <v>0</v>
-      </c>
-      <c r="U59">
-        <v>0</v>
-      </c>
-      <c r="V59">
-        <v>0</v>
-      </c>
-      <c r="W59">
-        <v>1</v>
-      </c>
-      <c r="X59">
-        <v>0</v>
-      </c>
-      <c r="Y59">
-        <v>0</v>
-      </c>
-      <c r="Z59">
-        <v>0</v>
-      </c>
-      <c r="AA59">
-        <v>0</v>
-      </c>
-      <c r="AB59">
-        <v>0</v>
-      </c>
-      <c r="AC59">
-        <v>0</v>
-      </c>
       <c r="AD59">
         <v>0</v>
       </c>
       <c r="AE59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF59">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG59" s="2">
-        <v>884.64043419267296</v>
+        <v>86.012392928740667</v>
       </c>
       <c r="AH59" s="1">
         <v>1</v>
@@ -7362,19 +7368,19 @@
     </row>
     <row r="60" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>10584</v>
+        <v>14443</v>
       </c>
       <c r="B60" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="C60">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="D60">
         <v>1</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -7389,7 +7395,7 @@
         <v>0</v>
       </c>
       <c r="J60">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K60">
         <v>0</v>
@@ -7398,7 +7404,7 @@
         <v>0</v>
       </c>
       <c r="M60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N60">
         <v>0</v>
@@ -7416,7 +7422,7 @@
         <v>0</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T60">
         <v>0</v>
@@ -7431,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="X60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y60">
         <v>0</v>
@@ -7440,7 +7446,7 @@
         <v>0</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB60">
         <v>0</v>
@@ -7452,13 +7458,13 @@
         <v>0</v>
       </c>
       <c r="AE60">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF60">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AG60" s="2">
-        <v>256.48553727161516</v>
+        <v>71.190999148325787</v>
       </c>
       <c r="AH60" s="1">
         <v>1</v>
@@ -7466,19 +7472,19 @@
     </row>
     <row r="61" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>14441</v>
+        <v>10818</v>
       </c>
       <c r="B61" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="C61">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D61">
         <v>1</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -7493,7 +7499,7 @@
         <v>0</v>
       </c>
       <c r="J61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K61">
         <v>0</v>
@@ -7511,10 +7517,10 @@
         <v>0</v>
       </c>
       <c r="P61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R61">
         <v>0</v>
@@ -7541,7 +7547,7 @@
         <v>0</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA61">
         <v>0</v>
@@ -7550,19 +7556,19 @@
         <v>0</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD61">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AE61">
+        <v>6</v>
+      </c>
+      <c r="AF61">
         <v>8</v>
       </c>
-      <c r="AF61">
-        <v>6</v>
-      </c>
       <c r="AG61" s="2">
-        <v>187.97268459240291</v>
+        <v>72.390953512350379</v>
       </c>
       <c r="AH61" s="1">
         <v>1</v>
@@ -7570,16 +7576,16 @@
     </row>
     <row r="62" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>5549</v>
+        <v>10574</v>
       </c>
       <c r="B62" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C62">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -7591,7 +7597,7 @@
         <v>0</v>
       </c>
       <c r="H62">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -7603,19 +7609,19 @@
         <v>0</v>
       </c>
       <c r="L62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62">
         <v>0</v>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -7624,7 +7630,7 @@
         <v>0</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62">
         <v>0</v>
@@ -7636,7 +7642,7 @@
         <v>0</v>
       </c>
       <c r="W62">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X62">
         <v>0</v>
@@ -7648,7 +7654,7 @@
         <v>0</v>
       </c>
       <c r="AA62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB62">
         <v>0</v>
@@ -7657,30 +7663,30 @@
         <v>0</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE62">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AF62">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG62" s="2">
-        <v>2020.6172839506173</v>
+        <v>94.175462028716197</v>
       </c>
       <c r="AH62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>10579</v>
+        <v>14445</v>
       </c>
       <c r="B63" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="C63">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -7713,7 +7719,7 @@
         <v>0</v>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -7725,10 +7731,10 @@
         <v>0</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T63">
         <v>0</v>
@@ -7755,22 +7761,22 @@
         <v>0</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD63">
         <v>0</v>
       </c>
       <c r="AE63">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF63">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG63" s="2">
-        <v>76.775383280300844</v>
+        <v>308.08317332459137</v>
       </c>
       <c r="AH63" s="1">
         <v>1</v>
@@ -7778,13 +7784,13 @@
     </row>
     <row r="64" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>5541</v>
+        <v>5512</v>
       </c>
       <c r="B64" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C64">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -7793,44 +7799,44 @@
         <v>0</v>
       </c>
       <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>1</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>0</v>
+      </c>
+      <c r="R64">
         <v>2</v>
       </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
-      <c r="H64">
-        <v>0</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>0</v>
-      </c>
-      <c r="K64">
-        <v>0</v>
-      </c>
-      <c r="L64">
-        <v>0</v>
-      </c>
-      <c r="M64">
-        <v>0</v>
-      </c>
-      <c r="N64">
-        <v>1</v>
-      </c>
-      <c r="O64">
-        <v>0</v>
-      </c>
-      <c r="P64">
-        <v>0</v>
-      </c>
-      <c r="Q64">
-        <v>0</v>
-      </c>
-      <c r="R64">
-        <v>0</v>
-      </c>
       <c r="S64">
         <v>0</v>
       </c>
@@ -7838,7 +7844,7 @@
         <v>0</v>
       </c>
       <c r="U64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V64">
         <v>0</v>
@@ -7853,10 +7859,10 @@
         <v>0</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB64">
         <v>0</v>
@@ -7868,7 +7874,7 @@
         <v>0</v>
       </c>
       <c r="AG64" s="2">
-        <v>81.16077812569344</v>
+        <v>850.61679790026244</v>
       </c>
       <c r="AH64" s="1">
         <v>1</v>
@@ -7876,13 +7882,13 @@
     </row>
     <row r="65" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>14448</v>
+        <v>5513</v>
       </c>
       <c r="B65" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="C65">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -7891,7 +7897,7 @@
         <v>0</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -7912,10 +7918,10 @@
         <v>0</v>
       </c>
       <c r="M65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -7924,7 +7930,7 @@
         <v>0</v>
       </c>
       <c r="Q65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R65">
         <v>0</v>
@@ -7951,7 +7957,7 @@
         <v>0</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA65">
         <v>0</v>
@@ -7966,13 +7972,13 @@
         <v>0</v>
       </c>
       <c r="AE65">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AF65">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AG65" s="2">
-        <v>66.340901679439099</v>
+        <v>381.26290941280615</v>
       </c>
       <c r="AH65" s="1">
         <v>1</v>
@@ -7980,13 +7986,13 @@
     </row>
     <row r="66" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>5483</v>
+        <v>5510</v>
       </c>
       <c r="B66" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C66">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -8046,37 +8052,37 @@
         <v>0</v>
       </c>
       <c r="W66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X66">
         <v>0</v>
       </c>
       <c r="Y66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z66">
         <v>0</v>
       </c>
       <c r="AA66">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB66">
         <v>0</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD66">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AE66">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AF66">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG66" s="2">
-        <v>74.255238358245023</v>
+        <v>115.98528065356714</v>
       </c>
       <c r="AH66" s="1">
         <v>1</v>
@@ -8084,16 +8090,16 @@
     </row>
     <row r="67" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>5528</v>
+        <v>14768</v>
       </c>
       <c r="B67" t="s">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="C67">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -8111,7 +8117,7 @@
         <v>0</v>
       </c>
       <c r="J67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67">
         <v>0</v>
@@ -8123,7 +8129,7 @@
         <v>0</v>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67">
         <v>0</v>
@@ -8141,7 +8147,7 @@
         <v>0</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U67">
         <v>0</v>
@@ -8165,22 +8171,22 @@
         <v>0</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD67">
         <v>0</v>
       </c>
       <c r="AE67">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AF67">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG67" s="2">
-        <v>142.27939575987114</v>
+        <v>107.59067742095107</v>
       </c>
       <c r="AH67" s="1">
         <v>1</v>
@@ -8188,13 +8194,13 @@
     </row>
     <row r="68" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>10570</v>
+        <v>14447</v>
       </c>
       <c r="B68" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="C68">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -8203,7 +8209,7 @@
         <v>0</v>
       </c>
       <c r="F68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -8227,7 +8233,7 @@
         <v>0</v>
       </c>
       <c r="N68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68">
         <v>0</v>
@@ -8248,7 +8254,7 @@
         <v>0</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V68">
         <v>1</v>
@@ -8269,7 +8275,7 @@
         <v>0</v>
       </c>
       <c r="AB68">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC68">
         <v>0</v>
@@ -8278,13 +8284,13 @@
         <v>0</v>
       </c>
       <c r="AE68">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AF68">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AG68" s="2">
-        <v>51.737912218074285</v>
+        <v>148.61082806874532</v>
       </c>
       <c r="AH68" s="1">
         <v>1</v>
@@ -8292,13 +8298,13 @@
     </row>
     <row r="69" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>10572</v>
+        <v>5527</v>
       </c>
       <c r="B69" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="C69">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -8313,7 +8319,7 @@
         <v>0</v>
       </c>
       <c r="H69">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -8340,10 +8346,10 @@
         <v>0</v>
       </c>
       <c r="Q69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -8355,7 +8361,7 @@
         <v>0</v>
       </c>
       <c r="V69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W69">
         <v>1</v>
@@ -8367,7 +8373,7 @@
         <v>0</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA69">
         <v>0</v>
@@ -8376,19 +8382,19 @@
         <v>0</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD69">
         <v>0</v>
       </c>
       <c r="AE69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF69">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG69" s="2">
-        <v>91.345402910898116</v>
+        <v>205.43578054262829</v>
       </c>
       <c r="AH69" s="1">
         <v>1</v>
@@ -8396,13 +8402,13 @@
     </row>
     <row r="70" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>14764</v>
+        <v>5537</v>
       </c>
       <c r="B70" t="s">
-        <v>95</v>
+        <v>31</v>
       </c>
       <c r="C70">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -8420,7 +8426,7 @@
         <v>0</v>
       </c>
       <c r="I70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70">
         <v>0</v>
@@ -8429,7 +8435,7 @@
         <v>0</v>
       </c>
       <c r="L70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70">
         <v>0</v>
@@ -8447,19 +8453,19 @@
         <v>0</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70">
         <v>0</v>
       </c>
       <c r="U70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W70">
         <v>0</v>
@@ -8471,7 +8477,7 @@
         <v>0</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA70">
         <v>0</v>
@@ -8486,13 +8492,13 @@
         <v>0</v>
       </c>
       <c r="AE70">
+        <v>7</v>
+      </c>
+      <c r="AF70">
         <v>8</v>
       </c>
-      <c r="AF70">
-        <v>5</v>
-      </c>
       <c r="AG70" s="2">
-        <v>108.13484120629838</v>
+        <v>110.01587408808433</v>
       </c>
       <c r="AH70" s="1">
         <v>1</v>
@@ -8500,13 +8506,13 @@
     </row>
     <row r="71" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>10573</v>
+        <v>14767</v>
       </c>
       <c r="B71" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="C71">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -8515,16 +8521,16 @@
         <v>0</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71">
         <v>0</v>
       </c>
       <c r="H71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71">
         <v>0</v>
@@ -8569,7 +8575,7 @@
         <v>0</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y71">
         <v>0</v>
@@ -8590,13 +8596,13 @@
         <v>0</v>
       </c>
       <c r="AE71">
+        <v>4</v>
+      </c>
+      <c r="AF71">
         <v>5</v>
       </c>
-      <c r="AF71">
-        <v>3</v>
-      </c>
       <c r="AG71" s="2">
-        <v>110.77965985929923</v>
+        <v>79.015716973117293</v>
       </c>
       <c r="AH71" s="1">
         <v>1</v>
@@ -8604,16 +8610,16 @@
     </row>
     <row r="72" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>5568</v>
+        <v>14437</v>
       </c>
       <c r="B72" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="C72">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -8631,7 +8637,7 @@
         <v>0</v>
       </c>
       <c r="J72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72">
         <v>0</v>
@@ -8643,13 +8649,13 @@
         <v>0</v>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O72">
         <v>0</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -8658,7 +8664,7 @@
         <v>0</v>
       </c>
       <c r="S72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T72">
         <v>0</v>
@@ -8667,19 +8673,19 @@
         <v>0</v>
       </c>
       <c r="V72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W72">
         <v>0</v>
       </c>
       <c r="X72">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y72">
         <v>0</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA72">
         <v>0</v>
@@ -8688,33 +8694,33 @@
         <v>0</v>
       </c>
       <c r="AC72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD72">
         <v>0</v>
       </c>
       <c r="AE72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF72">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AG72" s="2">
-        <v>1358.6843743515253</v>
+        <v>180.06082759005554</v>
       </c>
       <c r="AH72" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>5514</v>
+        <v>5573</v>
       </c>
       <c r="B73" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="C73">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -8729,10 +8735,10 @@
         <v>0</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -8741,7 +8747,7 @@
         <v>0</v>
       </c>
       <c r="L73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73">
         <v>0</v>
@@ -8762,10 +8768,10 @@
         <v>0</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T73">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U73">
         <v>1</v>
@@ -8798,13 +8804,13 @@
         <v>0</v>
       </c>
       <c r="AE73">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF73">
         <v>7</v>
       </c>
       <c r="AG73" s="2">
-        <v>726.66297731045938</v>
+        <v>113.92783106707424</v>
       </c>
       <c r="AH73" s="1">
         <v>1</v>
@@ -8812,19 +8818,19 @@
     </row>
     <row r="74" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>10571</v>
+        <v>5536</v>
       </c>
       <c r="B74" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="C74">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D74">
         <v>1</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -8836,10 +8842,10 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74">
         <v>0</v>
@@ -8851,13 +8857,13 @@
         <v>0</v>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O74">
         <v>0</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -8869,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="T74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U74">
         <v>0</v>
@@ -8893,7 +8899,7 @@
         <v>0</v>
       </c>
       <c r="AB74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -8902,13 +8908,13 @@
         <v>0</v>
       </c>
       <c r="AE74">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AF74">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AG74" s="2">
-        <v>57.85762896420308</v>
+        <v>884.64043419267296</v>
       </c>
       <c r="AH74" s="1">
         <v>1</v>
@@ -8916,13 +8922,13 @@
     </row>
     <row r="75" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>11398</v>
+        <v>10584</v>
       </c>
       <c r="B75" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C75">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -8940,10 +8946,10 @@
         <v>0</v>
       </c>
       <c r="I75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K75">
         <v>0</v>
@@ -8952,7 +8958,7 @@
         <v>0</v>
       </c>
       <c r="M75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N75">
         <v>0</v>
@@ -8970,7 +8976,7 @@
         <v>0</v>
       </c>
       <c r="S75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T75">
         <v>0</v>
@@ -8979,13 +8985,13 @@
         <v>0</v>
       </c>
       <c r="V75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W75">
         <v>0</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y75">
         <v>0</v>
@@ -8997,7 +9003,7 @@
         <v>0</v>
       </c>
       <c r="AB75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC75">
         <v>0</v>
@@ -9006,13 +9012,13 @@
         <v>0</v>
       </c>
       <c r="AE75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF75">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AG75" s="2">
-        <v>51.730456840605918</v>
+        <v>256.48553727161516</v>
       </c>
       <c r="AH75" s="1">
         <v>1</v>
@@ -9020,19 +9026,19 @@
     </row>
     <row r="76" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>10568</v>
+        <v>14441</v>
       </c>
       <c r="B76" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="C76">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="D76">
         <v>1</v>
       </c>
       <c r="E76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -9047,7 +9053,7 @@
         <v>0</v>
       </c>
       <c r="J76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76">
         <v>0</v>
@@ -9065,10 +9071,10 @@
         <v>0</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76">
         <v>0</v>
@@ -9077,7 +9083,7 @@
         <v>0</v>
       </c>
       <c r="T76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U76">
         <v>0</v>
@@ -9089,7 +9095,7 @@
         <v>0</v>
       </c>
       <c r="X76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y76">
         <v>0</v>
@@ -9107,16 +9113,16 @@
         <v>0</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE76">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF76">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AG76" s="2">
-        <v>84.691228530221579</v>
+        <v>187.97268459240291</v>
       </c>
       <c r="AH76" s="1">
         <v>1</v>
@@ -9124,13 +9130,13 @@
     </row>
     <row r="77" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>11298</v>
+        <v>10579</v>
       </c>
       <c r="B77" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C77">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -9145,7 +9151,7 @@
         <v>0</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -9166,19 +9172,19 @@
         <v>0</v>
       </c>
       <c r="O77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P77">
         <v>0</v>
       </c>
       <c r="Q77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R77">
         <v>0</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T77">
         <v>0</v>
@@ -9193,7 +9199,7 @@
         <v>0</v>
       </c>
       <c r="X77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y77">
         <v>0</v>
@@ -9208,19 +9214,19 @@
         <v>0</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD77">
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF77">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG77" s="2">
-        <v>162.93963519097048</v>
+        <v>76.775383280300844</v>
       </c>
       <c r="AH77" s="1">
         <v>1</v>
@@ -9228,22 +9234,22 @@
     </row>
     <row r="78" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>5500</v>
+        <v>5541</v>
       </c>
       <c r="B78" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C78">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78">
         <v>0</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -9264,7 +9270,7 @@
         <v>0</v>
       </c>
       <c r="M78">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N78">
         <v>1</v>
@@ -9279,7 +9285,7 @@
         <v>0</v>
       </c>
       <c r="R78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -9288,7 +9294,7 @@
         <v>0</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V78">
         <v>0</v>
@@ -9300,7 +9306,7 @@
         <v>0</v>
       </c>
       <c r="Y78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -9317,28 +9323,22 @@
       <c r="AD78">
         <v>0</v>
       </c>
-      <c r="AE78">
-        <v>4</v>
-      </c>
-      <c r="AF78">
-        <v>12</v>
-      </c>
       <c r="AG78" s="2">
-        <v>2478.1923076923076</v>
+        <v>81.16077812569344</v>
       </c>
       <c r="AH78" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>5547</v>
+        <v>14448</v>
       </c>
       <c r="B79" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="C79">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -9371,7 +9371,7 @@
         <v>0</v>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O79">
         <v>0</v>
@@ -9380,7 +9380,7 @@
         <v>0</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -9389,7 +9389,7 @@
         <v>0</v>
       </c>
       <c r="T79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U79">
         <v>0</v>
@@ -9401,7 +9401,7 @@
         <v>0</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y79">
         <v>0</v>
@@ -9416,27 +9416,33 @@
         <v>0</v>
       </c>
       <c r="AC79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD79">
         <v>0</v>
       </c>
+      <c r="AE79">
+        <v>7</v>
+      </c>
+      <c r="AF79">
+        <v>13</v>
+      </c>
       <c r="AG79" s="2">
-        <v>1249.1744163977985</v>
+        <v>66.340901679439099</v>
       </c>
       <c r="AH79" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>5557</v>
+        <v>5483</v>
       </c>
       <c r="B80" t="s">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="C80">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -9451,7 +9457,7 @@
         <v>0</v>
       </c>
       <c r="H80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -9475,41 +9481,41 @@
         <v>0</v>
       </c>
       <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>1</v>
+      </c>
+      <c r="R80">
+        <v>0</v>
+      </c>
+      <c r="S80">
+        <v>0</v>
+      </c>
+      <c r="T80">
+        <v>0</v>
+      </c>
+      <c r="U80">
+        <v>0</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>1</v>
+      </c>
+      <c r="X80">
+        <v>0</v>
+      </c>
+      <c r="Y80">
+        <v>1</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+      <c r="AA80">
         <v>2</v>
       </c>
-      <c r="Q80">
-        <v>0</v>
-      </c>
-      <c r="R80">
-        <v>0</v>
-      </c>
-      <c r="S80">
-        <v>0</v>
-      </c>
-      <c r="T80">
-        <v>0</v>
-      </c>
-      <c r="U80">
-        <v>1</v>
-      </c>
-      <c r="V80">
-        <v>0</v>
-      </c>
-      <c r="W80">
-        <v>0</v>
-      </c>
-      <c r="X80">
-        <v>0</v>
-      </c>
-      <c r="Y80">
-        <v>0</v>
-      </c>
-      <c r="Z80">
-        <v>0</v>
-      </c>
-      <c r="AA80">
-        <v>0</v>
-      </c>
       <c r="AB80">
         <v>0</v>
       </c>
@@ -9517,16 +9523,16 @@
         <v>0</v>
       </c>
       <c r="AD80">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF80">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG80" s="2">
-        <v>103.99037848859437</v>
+        <v>74.255238358245023</v>
       </c>
       <c r="AH80" s="1">
         <v>1</v>
@@ -9534,16 +9540,16 @@
     </row>
     <row r="81" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>5569</v>
+        <v>10570</v>
       </c>
       <c r="B81" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C81">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -9561,7 +9567,7 @@
         <v>0</v>
       </c>
       <c r="J81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K81">
         <v>0</v>
@@ -9594,10 +9600,10 @@
         <v>0</v>
       </c>
       <c r="U81">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W81">
         <v>0</v>
@@ -9615,36 +9621,36 @@
         <v>0</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC81">
         <v>0</v>
       </c>
       <c r="AD81">
+        <v>0</v>
+      </c>
+      <c r="AE81">
+        <v>2</v>
+      </c>
+      <c r="AF81">
         <v>5</v>
       </c>
-      <c r="AE81">
-        <v>3</v>
-      </c>
-      <c r="AF81">
-        <v>10</v>
-      </c>
       <c r="AG81" s="2">
-        <v>3640.5283867341213</v>
+        <v>51.737912218074285</v>
       </c>
       <c r="AH81" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>14762</v>
+        <v>10572</v>
       </c>
       <c r="B82" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="C82">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -9659,7 +9665,7 @@
         <v>0</v>
       </c>
       <c r="H82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -9668,7 +9674,7 @@
         <v>0</v>
       </c>
       <c r="K82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -9683,10 +9689,10 @@
         <v>0</v>
       </c>
       <c r="P82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82">
         <v>0</v>
@@ -9701,10 +9707,10 @@
         <v>0</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X82">
         <v>0</v>
@@ -9719,7 +9725,7 @@
         <v>0</v>
       </c>
       <c r="AB82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC82">
         <v>0</v>
@@ -9728,33 +9734,33 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AF82">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AG82" s="2">
-        <v>1480.659090909091</v>
+        <v>91.345402910898116</v>
       </c>
       <c r="AH82" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>14444</v>
+        <v>14764</v>
       </c>
       <c r="B83" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C83">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D83">
         <v>1</v>
       </c>
       <c r="E83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -9766,16 +9772,16 @@
         <v>0</v>
       </c>
       <c r="I83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83">
         <v>0</v>
       </c>
       <c r="K83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83">
         <v>0</v>
@@ -9784,7 +9790,7 @@
         <v>0</v>
       </c>
       <c r="O83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P83">
         <v>0</v>
@@ -9802,7 +9808,7 @@
         <v>0</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V83">
         <v>0</v>
@@ -9829,16 +9835,16 @@
         <v>0</v>
       </c>
       <c r="AD83">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AE83">
         <v>8</v>
       </c>
       <c r="AF83">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AG83" s="2">
-        <v>110.3080831330026</v>
+        <v>108.13484120629838</v>
       </c>
       <c r="AH83" s="1">
         <v>1</v>
@@ -9846,14 +9852,14 @@
     </row>
     <row r="84" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>10816</v>
+        <v>10573</v>
       </c>
       <c r="B84" t="s">
+        <v>62</v>
+      </c>
+      <c r="C84">
         <v>70</v>
       </c>
-      <c r="C84">
-        <v>83</v>
-      </c>
       <c r="D84">
         <v>1</v>
       </c>
@@ -9861,16 +9867,16 @@
         <v>0</v>
       </c>
       <c r="F84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84">
         <v>0</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -9882,13 +9888,13 @@
         <v>0</v>
       </c>
       <c r="M84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N84">
         <v>0</v>
       </c>
       <c r="O84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P84">
         <v>0</v>
@@ -9897,7 +9903,7 @@
         <v>0</v>
       </c>
       <c r="R84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -9935,8 +9941,14 @@
       <c r="AD84">
         <v>0</v>
       </c>
+      <c r="AE84">
+        <v>5</v>
+      </c>
+      <c r="AF84">
+        <v>3</v>
+      </c>
       <c r="AG84" s="2">
-        <v>192.3913363783704</v>
+        <v>110.77965985929923</v>
       </c>
       <c r="AH84" s="1">
         <v>1</v>
@@ -9944,13 +9956,13 @@
     </row>
     <row r="85" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>10576</v>
+        <v>5514</v>
       </c>
       <c r="B85" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="C85">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -9959,7 +9971,7 @@
         <v>0</v>
       </c>
       <c r="F85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -9968,16 +9980,16 @@
         <v>0</v>
       </c>
       <c r="I85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85">
         <v>0</v>
       </c>
       <c r="K85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85">
         <v>0</v>
@@ -9998,13 +10010,13 @@
         <v>0</v>
       </c>
       <c r="S85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V85">
         <v>0</v>
@@ -10034,33 +10046,33 @@
         <v>0</v>
       </c>
       <c r="AE85">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AF85">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AG85" s="2">
-        <v>1932.0141760189015</v>
+        <v>726.66297731045938</v>
       </c>
       <c r="AH85" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>5521</v>
+        <v>10571</v>
       </c>
       <c r="B86" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="C86">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D86">
         <v>1</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -10096,7 +10108,7 @@
         <v>0</v>
       </c>
       <c r="Q86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R86">
         <v>0</v>
@@ -10105,7 +10117,7 @@
         <v>0</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U86">
         <v>0</v>
@@ -10114,7 +10126,7 @@
         <v>0</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X86">
         <v>0</v>
@@ -10129,16 +10141,22 @@
         <v>0</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD86">
         <v>0</v>
       </c>
+      <c r="AE86">
+        <v>6</v>
+      </c>
+      <c r="AF86">
+        <v>9</v>
+      </c>
       <c r="AG86" s="2">
-        <v>270.93761520501374</v>
+        <v>57.85762896420308</v>
       </c>
       <c r="AH86" s="1">
         <v>1</v>
@@ -10146,16 +10164,16 @@
     </row>
     <row r="87" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>5533</v>
+        <v>11398</v>
       </c>
       <c r="B87" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="C87">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -10167,10 +10185,10 @@
         <v>0</v>
       </c>
       <c r="H87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -10191,16 +10209,16 @@
         <v>0</v>
       </c>
       <c r="P87">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R87">
         <v>0</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T87">
         <v>0</v>
@@ -10227,7 +10245,7 @@
         <v>0</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC87">
         <v>0</v>
@@ -10236,36 +10254,36 @@
         <v>0</v>
       </c>
       <c r="AE87">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF87">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG87" s="2">
-        <v>1709.4712525667351</v>
+        <v>51.730456840605918</v>
       </c>
       <c r="AH87" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>14436</v>
+        <v>10568</v>
       </c>
       <c r="B88" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="C88">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -10292,10 +10310,10 @@
         <v>0</v>
       </c>
       <c r="O88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -10307,7 +10325,7 @@
         <v>0</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U88">
         <v>0</v>
@@ -10319,7 +10337,7 @@
         <v>0</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y88">
         <v>0</v>
@@ -10328,7 +10346,7 @@
         <v>0</v>
       </c>
       <c r="AA88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB88">
         <v>0</v>
@@ -10340,27 +10358,27 @@
         <v>0</v>
       </c>
       <c r="AE88">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF88">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG88" s="2">
-        <v>2195.8404950154691</v>
+        <v>84.691228530221579</v>
       </c>
       <c r="AH88" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>5497</v>
+        <v>11298</v>
       </c>
       <c r="B89" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="C89">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -10375,7 +10393,7 @@
         <v>0</v>
       </c>
       <c r="H89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -10396,13 +10414,13 @@
         <v>0</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P89">
         <v>0</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R89">
         <v>0</v>
@@ -10423,7 +10441,7 @@
         <v>0</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y89">
         <v>0</v>
@@ -10441,10 +10459,16 @@
         <v>0</v>
       </c>
       <c r="AD89">
+        <v>0</v>
+      </c>
+      <c r="AE89">
         <v>9</v>
       </c>
+      <c r="AF89">
+        <v>5</v>
+      </c>
       <c r="AG89" s="2">
-        <v>660.68944963242598</v>
+        <v>162.93963519097048</v>
       </c>
       <c r="AH89" s="1">
         <v>1</v>
@@ -10452,13 +10476,13 @@
     </row>
     <row r="90" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>11395</v>
+        <v>5547</v>
       </c>
       <c r="B90" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="C90">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -10497,7 +10521,7 @@
         <v>0</v>
       </c>
       <c r="P90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -10506,10 +10530,10 @@
         <v>0</v>
       </c>
       <c r="S90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U90">
         <v>0</v>
@@ -10527,28 +10551,22 @@
         <v>0</v>
       </c>
       <c r="Z90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA90">
         <v>0</v>
       </c>
       <c r="AB90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD90">
         <v>0</v>
       </c>
-      <c r="AE90">
-        <v>9</v>
-      </c>
-      <c r="AF90">
-        <v>6</v>
-      </c>
       <c r="AG90" s="2">
-        <v>1816.413043478261</v>
+        <v>1249.1744163977985</v>
       </c>
       <c r="AH90" s="1">
         <v>0</v>
@@ -10556,13 +10574,13 @@
     </row>
     <row r="91" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>11396</v>
+        <v>5557</v>
       </c>
       <c r="B91" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="C91">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -10577,7 +10595,7 @@
         <v>0</v>
       </c>
       <c r="H91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -10586,7 +10604,7 @@
         <v>0</v>
       </c>
       <c r="K91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -10595,13 +10613,13 @@
         <v>0</v>
       </c>
       <c r="N91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O91">
         <v>0</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -10616,10 +10634,10 @@
         <v>0</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W91">
         <v>0</v>
@@ -10643,30 +10661,30 @@
         <v>0</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE91">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AF91">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG91" s="2">
-        <v>1455.2972143013817</v>
+        <v>103.99037848859437</v>
       </c>
       <c r="AH91" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>5567</v>
+        <v>14762</v>
       </c>
       <c r="B92" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="C92">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -10684,13 +10702,13 @@
         <v>0</v>
       </c>
       <c r="I92">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J92">
         <v>0</v>
       </c>
       <c r="K92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -10705,7 +10723,7 @@
         <v>0</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -10717,7 +10735,7 @@
         <v>0</v>
       </c>
       <c r="T92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U92">
         <v>0</v>
@@ -10738,10 +10756,10 @@
         <v>0</v>
       </c>
       <c r="AA92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC92">
         <v>0</v>
@@ -10750,33 +10768,33 @@
         <v>0</v>
       </c>
       <c r="AE92">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF92">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AG92" s="2">
-        <v>786.98246032692998</v>
+        <v>1480.659090909091</v>
       </c>
       <c r="AH92" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>14440</v>
+        <v>14444</v>
       </c>
       <c r="B93" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C93">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -10794,13 +10812,13 @@
         <v>0</v>
       </c>
       <c r="K93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93">
         <v>0</v>
       </c>
       <c r="M93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N93">
         <v>0</v>
@@ -10824,7 +10842,7 @@
         <v>0</v>
       </c>
       <c r="U93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V93">
         <v>0</v>
@@ -10845,36 +10863,36 @@
         <v>0</v>
       </c>
       <c r="AB93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC93">
         <v>0</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AE93">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF93">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG93" s="2">
-        <v>3271.7664092664095</v>
+        <v>110.3080831330026</v>
       </c>
       <c r="AH93" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>5565</v>
+        <v>10816</v>
       </c>
       <c r="B94" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="C94">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -10883,7 +10901,7 @@
         <v>0</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -10904,13 +10922,13 @@
         <v>0</v>
       </c>
       <c r="M94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N94">
         <v>0</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P94">
         <v>0</v>
@@ -10919,13 +10937,13 @@
         <v>0</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S94">
         <v>0</v>
       </c>
       <c r="T94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U94">
         <v>0</v>
@@ -10946,7 +10964,7 @@
         <v>0</v>
       </c>
       <c r="AA94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB94">
         <v>0</v>
@@ -10955,39 +10973,33 @@
         <v>0</v>
       </c>
       <c r="AD94">
-        <v>15</v>
-      </c>
-      <c r="AE94">
-        <v>6</v>
-      </c>
-      <c r="AF94">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AG94" s="2">
-        <v>2148.2701264138395</v>
+        <v>192.3913363783704</v>
       </c>
       <c r="AH94" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>5543</v>
+        <v>10576</v>
       </c>
       <c r="B95" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C95">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95">
         <v>0</v>
       </c>
       <c r="F95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -11002,10 +11014,10 @@
         <v>0</v>
       </c>
       <c r="K95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95">
         <v>0</v>
@@ -11023,10 +11035,10 @@
         <v>0</v>
       </c>
       <c r="R95">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T95">
         <v>0</v>
@@ -11035,7 +11047,7 @@
         <v>0</v>
       </c>
       <c r="V95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W95">
         <v>0</v>
@@ -11056,19 +11068,19 @@
         <v>0</v>
       </c>
       <c r="AC95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD95">
         <v>0</v>
       </c>
       <c r="AE95">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF95">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AG95" s="2">
-        <v>3888.6512180629838</v>
+        <v>1932.0141760189015</v>
       </c>
       <c r="AH95" s="1">
         <v>0</v>
@@ -11076,16 +11088,16 @@
     </row>
     <row r="96" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>5556</v>
+        <v>5521</v>
       </c>
       <c r="B96" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C96">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -11103,28 +11115,28 @@
         <v>0</v>
       </c>
       <c r="J96">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96">
         <v>0</v>
       </c>
       <c r="M96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N96">
         <v>0</v>
       </c>
       <c r="O96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P96">
         <v>0</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96">
         <v>0</v>
@@ -11160,36 +11172,30 @@
         <v>0</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD96">
-        <v>4</v>
-      </c>
-      <c r="AE96">
-        <v>5</v>
-      </c>
-      <c r="AF96">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AG96" s="2">
-        <v>2822.6678291194416</v>
+        <v>270.93761520501374</v>
       </c>
       <c r="AH96" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>5566</v>
+        <v>5497</v>
       </c>
       <c r="B97" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="C97">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -11237,7 +11243,7 @@
         <v>0</v>
       </c>
       <c r="T97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U97">
         <v>0</v>
@@ -11264,36 +11270,30 @@
         <v>0</v>
       </c>
       <c r="AC97">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD97">
-        <v>0</v>
-      </c>
-      <c r="AE97">
-        <v>2</v>
-      </c>
-      <c r="AF97">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG97" s="2">
-        <v>3396.2848297213632</v>
+        <v>660.68944963242598</v>
       </c>
       <c r="AH97" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>14442</v>
+        <v>11395</v>
       </c>
       <c r="B98" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C98">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -11323,22 +11323,22 @@
         <v>0</v>
       </c>
       <c r="N98">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O98">
         <v>0</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q98">
         <v>0</v>
       </c>
       <c r="R98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T98">
         <v>0</v>
@@ -11353,19 +11353,19 @@
         <v>0</v>
       </c>
       <c r="X98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y98">
         <v>0</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA98">
         <v>0</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC98">
         <v>0</v>
@@ -11374,13 +11374,13 @@
         <v>0</v>
       </c>
       <c r="AE98">
+        <v>9</v>
+      </c>
+      <c r="AF98">
         <v>6</v>
       </c>
-      <c r="AF98">
-        <v>12</v>
-      </c>
       <c r="AG98" s="2">
-        <v>2358.7956204379561</v>
+        <v>1816.413043478261</v>
       </c>
       <c r="AH98" s="1">
         <v>0</v>
@@ -11388,22 +11388,22 @@
     </row>
     <row r="99" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>14446</v>
+        <v>11396</v>
       </c>
       <c r="B99" t="s">
+        <v>75</v>
+      </c>
+      <c r="C99">
         <v>90</v>
       </c>
-      <c r="C99">
-        <v>98</v>
-      </c>
       <c r="D99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99">
         <v>0</v>
       </c>
       <c r="F99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>0</v>
       </c>
       <c r="K99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99">
         <v>0</v>
@@ -11445,19 +11445,19 @@
         <v>0</v>
       </c>
       <c r="T99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U99">
         <v>0</v>
       </c>
       <c r="V99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W99">
         <v>0</v>
       </c>
       <c r="X99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y99">
         <v>0</v>
@@ -11475,16 +11475,16 @@
         <v>0</v>
       </c>
       <c r="AD99">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AE99">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF99">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="AG99" s="2">
-        <v>3231.1817279046672</v>
+        <v>1455.2972143013817</v>
       </c>
       <c r="AH99" s="1">
         <v>0</v>
@@ -11492,16 +11492,16 @@
     </row>
     <row r="100" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>5518</v>
+        <v>5567</v>
       </c>
       <c r="B100" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="C100">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -11516,7 +11516,7 @@
         <v>0</v>
       </c>
       <c r="I100">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -11528,7 +11528,7 @@
         <v>0</v>
       </c>
       <c r="M100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N100">
         <v>0</v>
@@ -11549,7 +11549,7 @@
         <v>0</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U100">
         <v>0</v>
@@ -11561,16 +11561,16 @@
         <v>0</v>
       </c>
       <c r="X100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y100">
         <v>0</v>
       </c>
       <c r="Z100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB100">
         <v>0</v>
@@ -11582,30 +11582,30 @@
         <v>0</v>
       </c>
       <c r="AE100">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AF100">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AG100" s="2">
-        <v>3217.4737893160259</v>
+        <v>786.98246032692998</v>
       </c>
       <c r="AH100" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>14191</v>
+        <v>5565</v>
       </c>
       <c r="B101" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="C101">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -11626,13 +11626,13 @@
         <v>0</v>
       </c>
       <c r="K101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101">
         <v>0</v>
       </c>
       <c r="M101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N101">
         <v>0</v>
@@ -11653,13 +11653,13 @@
         <v>0</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U101">
         <v>0</v>
       </c>
       <c r="V101">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W101">
         <v>0</v>
@@ -11674,34 +11674,33 @@
         <v>0</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC101">
         <v>0</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE101">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF101">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AG101" s="2">
-        <v>4090.1774397972126</v>
+        <v>2148.2701264138395</v>
       </c>
       <c r="AH101" s="1">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:AF101">
-    <sortCondition ref="C2:C101"/>
-    <sortCondition ref="A2:A101"/>
+  <sortState ref="A2:AH101">
+    <sortCondition ref="D2:D101"/>
   </sortState>
   <conditionalFormatting sqref="D1:D1048576">
     <cfRule type="colorScale" priority="3">
